--- a/public/templates/3_Litmus_Packages_Bulk_Template.xlsx
+++ b/public/templates/3_Litmus_Packages_Bulk_Template.xlsx
@@ -489,7 +489,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="123" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
